--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -3503,7 +3503,7 @@
         <v>0.06382599393831342</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -7051,7 +7051,7 @@
         <v>-0.0008710501321338759</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>103148</v>
@@ -10599,7 +10599,7 @@
         <v>0.0139785445595133</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>41946</v>
@@ -14147,7 +14147,7 @@
         <v>0.00132150892291562</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>66160</v>
@@ -17214,7 +17214,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -23385,7 +23385,7 @@
         <v>0.01552548811193685</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>152356</v>
@@ -26465,7 +26465,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -29791,7 +29791,7 @@
         <v>0.001466582861931699</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>135985</v>
@@ -32858,7 +32858,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -35481,7 +35481,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -37216,7 +37216,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -39543,7 +39543,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>26891</v>
@@ -43091,7 +43091,7 @@
         <v>0.01884432202903541</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>63879</v>
@@ -46158,7 +46158,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -3503,7 +3503,7 @@
         <v>0.06382599393831342</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -7051,7 +7051,7 @@
         <v>-0.0008710501321338759</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
         <v>103148</v>
@@ -7069,7 +7069,7 @@
         <v>13386</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -10599,7 +10599,7 @@
         <v>0.0139785445595133</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
         <v>41946</v>
@@ -10617,7 +10617,7 @@
         <v>4507</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -14147,7 +14147,7 @@
         <v>0.00132150892291562</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
         <v>66160</v>
@@ -17214,7 +17214,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -23385,7 +23385,7 @@
         <v>0.01552548811193685</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
         <v>152356</v>
@@ -26465,7 +26465,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -29791,7 +29791,7 @@
         <v>0.001466582861931699</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
         <v>135985</v>
@@ -32858,7 +32858,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -35481,7 +35481,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -37216,7 +37216,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -39543,7 +39543,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
         <v>26891</v>
@@ -43091,7 +43091,7 @@
         <v>0.01884432202903541</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
         <v>63879</v>
@@ -46158,7 +46158,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -3503,7 +3503,7 @@
         <v>0.06382599393831342</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -7051,7 +7051,7 @@
         <v>-0.0008710501321338759</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>103148</v>
@@ -7066,10 +7066,10 @@
         <v>0.05455810447790039</v>
       </c>
       <c r="J56" t="n">
-        <v>13386</v>
+        <v>13384</v>
       </c>
       <c r="K56" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="57">
@@ -10599,7 +10599,7 @@
         <v>0.0139785445595133</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>41946</v>
@@ -14147,7 +14147,7 @@
         <v>0.00132150892291562</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>66160</v>
@@ -17214,7 +17214,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -23385,7 +23385,7 @@
         <v>0.01552548811193685</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>152356</v>
@@ -23403,7 +23403,7 @@
         <v>16912</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="57">
@@ -26465,7 +26465,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -29791,7 +29791,7 @@
         <v>0.001466582861931699</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>135985</v>
@@ -32858,7 +32858,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -35481,7 +35481,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -37216,7 +37216,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -39543,7 +39543,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>26891</v>
@@ -43091,7 +43091,7 @@
         <v>0.01884432202903541</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>63879</v>
@@ -46158,7 +46158,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -7066,10 +7066,10 @@
         <v>0.05455810447790039</v>
       </c>
       <c r="J56" t="n">
-        <v>13384</v>
+        <v>13392</v>
       </c>
       <c r="K56" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -23400,10 +23400,10 @@
         <v>0.4900090139288228</v>
       </c>
       <c r="J56" t="n">
-        <v>16912</v>
+        <v>16929</v>
       </c>
       <c r="K56" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -29809,7 +29809,7 @@
         <v>11523</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57">
@@ -35499,7 +35499,7 @@
         <v>141</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -29809,7 +29809,7 @@
         <v>11523</v>
       </c>
       <c r="K56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="57">
@@ -43109,7 +43109,7 @@
         <v>5617</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -29809,7 +29809,7 @@
         <v>11523</v>
       </c>
       <c r="K56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57">
@@ -37234,7 +37234,7 @@
         <v>637</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -3503,7 +3503,7 @@
         <v>0.06382599393831342</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -7051,7 +7051,7 @@
         <v>-0.0008710501321338759</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F56" t="n">
         <v>103148</v>
@@ -7066,10 +7066,10 @@
         <v>0.05455810447790039</v>
       </c>
       <c r="J56" t="n">
-        <v>13392</v>
+        <v>13390</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -10599,7 +10599,7 @@
         <v>0.0139785445595133</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F56" t="n">
         <v>41946</v>
@@ -14147,7 +14147,7 @@
         <v>0.00132150892291562</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F56" t="n">
         <v>66160</v>
@@ -17214,7 +17214,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -23385,7 +23385,7 @@
         <v>0.01552548811193685</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F56" t="n">
         <v>152356</v>
@@ -23403,7 +23403,7 @@
         <v>16929</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57">
@@ -26465,7 +26465,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -29791,7 +29791,7 @@
         <v>0.001466582861931699</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F56" t="n">
         <v>135985</v>
@@ -32858,7 +32858,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -35481,7 +35481,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -37216,7 +37216,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -39543,7 +39543,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F56" t="n">
         <v>26891</v>
@@ -43091,7 +43091,7 @@
         <v>0.01884432202903541</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F56" t="n">
         <v>63879</v>
@@ -43109,7 +43109,7 @@
         <v>5617</v>
       </c>
       <c r="K56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -46158,7 +46158,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -3503,7 +3503,7 @@
         <v>0.06382599393831342</v>
       </c>
       <c r="E56" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -7051,7 +7051,7 @@
         <v>-0.0008710501321338759</v>
       </c>
       <c r="E56" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F56" t="n">
         <v>103148</v>
@@ -7069,7 +7069,7 @@
         <v>13390</v>
       </c>
       <c r="K56" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57">
@@ -10599,7 +10599,7 @@
         <v>0.0139785445595133</v>
       </c>
       <c r="E56" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F56" t="n">
         <v>41946</v>
@@ -14147,7 +14147,7 @@
         <v>0.00132150892291562</v>
       </c>
       <c r="E56" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F56" t="n">
         <v>66160</v>
@@ -17214,7 +17214,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -23385,7 +23385,7 @@
         <v>0.01552548811193685</v>
       </c>
       <c r="E56" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F56" t="n">
         <v>152356</v>
@@ -23403,7 +23403,7 @@
         <v>16929</v>
       </c>
       <c r="K56" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57">
@@ -26465,7 +26465,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -29791,7 +29791,7 @@
         <v>0.001466582861931699</v>
       </c>
       <c r="E56" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F56" t="n">
         <v>135985</v>
@@ -29809,7 +29809,7 @@
         <v>11523</v>
       </c>
       <c r="K56" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="57">
@@ -32858,7 +32858,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -35481,7 +35481,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -37216,7 +37216,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -39543,7 +39543,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F56" t="n">
         <v>26891</v>
@@ -43091,7 +43091,7 @@
         <v>0.01884432202903541</v>
       </c>
       <c r="E56" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F56" t="n">
         <v>63879</v>
@@ -46158,7 +46158,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -7066,10 +7066,10 @@
         <v>0.05455810447790039</v>
       </c>
       <c r="J56" t="n">
-        <v>13390</v>
+        <v>13396</v>
       </c>
       <c r="K56" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -23400,10 +23400,10 @@
         <v>0.4900090139288228</v>
       </c>
       <c r="J56" t="n">
-        <v>16929</v>
+        <v>16937</v>
       </c>
       <c r="K56" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -29806,10 +29806,10 @@
         <v>0.0004769417030487581</v>
       </c>
       <c r="J56" t="n">
-        <v>11523</v>
+        <v>11539</v>
       </c>
       <c r="K56" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -35496,10 +35496,10 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -37231,10 +37231,10 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -3503,7 +3503,7 @@
         <v>0.06382599393831342</v>
       </c>
       <c r="E56" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -7042,16 +7042,16 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>203026</v>
+        <v>203354</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>-0.0008710501321338759</v>
+        <v>0.000743099265266753</v>
       </c>
       <c r="E56" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F56" t="n">
         <v>103148</v>
@@ -7066,7 +7066,7 @@
         <v>0.05455810447790039</v>
       </c>
       <c r="J56" t="n">
-        <v>13396</v>
+        <v>13431</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -7085,7 +7085,7 @@
         <v>0</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>-0.0546629495729611</v>
+        <v>-0.05618773173874131</v>
       </c>
       <c r="E57" t="n">
         <v>2</v>
@@ -10590,16 +10590,16 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>87336</v>
+        <v>87580</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0.0139785445595133</v>
+        <v>0.016811405749315</v>
       </c>
       <c r="E56" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F56" t="n">
         <v>41946</v>
@@ -10614,10 +10614,10 @@
         <v>1.238313767342583</v>
       </c>
       <c r="J56" t="n">
-        <v>4507</v>
+        <v>4510</v>
       </c>
       <c r="K56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -10633,7 +10633,7 @@
         <v>0</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>-0.09352386186681323</v>
+        <v>-0.09604932633021238</v>
       </c>
       <c r="E57" t="n">
         <v>2</v>
@@ -14147,7 +14147,7 @@
         <v>0.00132150892291562</v>
       </c>
       <c r="E56" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F56" t="n">
         <v>66160</v>
@@ -14162,7 +14162,7 @@
         <v>0.0008733098443099346</v>
       </c>
       <c r="J56" t="n">
-        <v>5122</v>
+        <v>5139</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -17214,7 +17214,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -23385,7 +23385,7 @@
         <v>0.01552548811193685</v>
       </c>
       <c r="E56" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F56" t="n">
         <v>152356</v>
@@ -23394,16 +23394,16 @@
         <v>4948</v>
       </c>
       <c r="H56" t="n">
-        <v>69158</v>
+        <v>70983</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.4900090139288228</v>
+        <v>0.5020166198424866</v>
       </c>
       <c r="J56" t="n">
-        <v>16937</v>
+        <v>17024</v>
       </c>
       <c r="K56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -23434,7 +23434,7 @@
         <v>0</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>-0.8791364555642889</v>
+        <v>-0.8801026777696496</v>
       </c>
       <c r="J57" t="n">
         <v>9274</v>
@@ -26465,7 +26465,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -29782,16 +29782,16 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>157740</v>
+        <v>157996</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0.001466582861931699</v>
+        <v>0.003091886812817045</v>
       </c>
       <c r="E56" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F56" t="n">
         <v>135985</v>
@@ -29806,7 +29806,7 @@
         <v>0.0004769417030487581</v>
       </c>
       <c r="J56" t="n">
-        <v>11539</v>
+        <v>11568</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -29825,7 +29825,7 @@
         <v>0</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>-0.203347280334728</v>
+        <v>-0.2046380921035976</v>
       </c>
       <c r="E57" t="n">
         <v>2</v>
@@ -32858,7 +32858,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -35481,7 +35481,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -37216,7 +37216,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -39543,7 +39543,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F56" t="n">
         <v>26891</v>
@@ -39558,7 +39558,7 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>1845</v>
+        <v>1847</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -43091,7 +43091,7 @@
         <v>0.01884432202903541</v>
       </c>
       <c r="E56" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F56" t="n">
         <v>63879</v>
@@ -43106,10 +43106,10 @@
         <v>0.001236713160819675</v>
       </c>
       <c r="J56" t="n">
-        <v>5617</v>
+        <v>5630</v>
       </c>
       <c r="K56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -46158,7 +46158,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -23400,7 +23400,7 @@
         <v>0.5020166198424866</v>
       </c>
       <c r="J56" t="n">
-        <v>17024</v>
+        <v>17026</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -43106,7 +43106,7 @@
         <v>0.001236713160819675</v>
       </c>
       <c r="J56" t="n">
-        <v>5630</v>
+        <v>5631</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -3799,7 +3799,7 @@
         <v>0.03468007629616785</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -7384,7 +7384,7 @@
         <v>0.0006544599229410346</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
         <v>103148</v>
@@ -10969,7 +10969,7 @@
         <v>0.016811405749315</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
         <v>41946</v>
@@ -14554,7 +14554,7 @@
         <v>0.006598449748578204</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
         <v>66160</v>
@@ -17584,7 +17584,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -20466,7 +20466,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -23903,7 +23903,7 @@
         <v>0.0123151211971201</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
         <v>152356</v>
@@ -26946,7 +26946,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -30383,7 +30383,7 @@
         <v>0.002430002601308268</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
         <v>135985</v>
@@ -33413,7 +33413,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -36073,7 +36073,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -37697,7 +37697,7 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -40283,7 +40283,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
         <v>26891</v>
@@ -43868,7 +43868,7 @@
         <v>0.01884432202903541</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
         <v>63879</v>
@@ -46898,7 +46898,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -3799,7 +3799,7 @@
         <v>0.03468007629616785</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -7384,7 +7384,7 @@
         <v>0.0006544599229410346</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F64" t="n">
         <v>103148</v>
@@ -7399,7 +7399,7 @@
         <v>0.01866855841391928</v>
       </c>
       <c r="J64" t="n">
-        <v>13431</v>
+        <v>13430</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -10969,7 +10969,7 @@
         <v>0.016811405749315</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F64" t="n">
         <v>41946</v>
@@ -14554,7 +14554,7 @@
         <v>0.006598449748578204</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F64" t="n">
         <v>66160</v>
@@ -17584,7 +17584,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -20466,7 +20466,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -23903,7 +23903,7 @@
         <v>0.0123151211971201</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F64" t="n">
         <v>152356</v>
@@ -26946,7 +26946,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -30383,7 +30383,7 @@
         <v>0.002430002601308268</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F64" t="n">
         <v>135985</v>
@@ -33413,7 +33413,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -36073,7 +36073,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -37697,7 +37697,7 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -40283,7 +40283,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F64" t="n">
         <v>26891</v>
@@ -43868,7 +43868,7 @@
         <v>0.01884432202903541</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F64" t="n">
         <v>63879</v>
@@ -46898,7 +46898,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -7375,13 +7375,13 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>203354</v>
+        <v>203367</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0.0006544599229410346</v>
+        <v>0.0007184296898450456</v>
       </c>
       <c r="E64" t="n">
         <v>2</v>
@@ -7402,7 +7402,7 @@
         <v>13430</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
@@ -7418,7 +7418,7 @@
         <v>0</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>-0.05618773173874131</v>
+        <v>-0.05624806384516662</v>
       </c>
       <c r="E65" t="n">
         <v>5</v>
@@ -10987,7 +10987,7 @@
         <v>4510</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -7402,7 +7402,7 @@
         <v>13430</v>
       </c>
       <c r="K64" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65">
@@ -10987,7 +10987,7 @@
         <v>4510</v>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -23921,7 +23921,7 @@
         <v>17026</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -10987,7 +10987,7 @@
         <v>4510</v>
       </c>
       <c r="K64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -3799,7 +3799,7 @@
         <v>0.03468007629616785</v>
       </c>
       <c r="E64" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -7384,7 +7384,7 @@
         <v>0.0007184296898450456</v>
       </c>
       <c r="E64" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>103148</v>
@@ -7399,10 +7399,10 @@
         <v>0.01866855841391928</v>
       </c>
       <c r="J64" t="n">
-        <v>13430</v>
+        <v>13439</v>
       </c>
       <c r="K64" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -10960,16 +10960,16 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>87580</v>
+        <v>87636</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0.016811405749315</v>
+        <v>0.01746157061254818</v>
       </c>
       <c r="E64" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>41946</v>
@@ -10984,10 +10984,10 @@
         <v>1.238313767342583</v>
       </c>
       <c r="J64" t="n">
-        <v>4510</v>
+        <v>4516</v>
       </c>
       <c r="K64" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -11003,7 +11003,7 @@
         <v>0</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>-0.08770267184288651</v>
+        <v>-0.08828563603998357</v>
       </c>
       <c r="E65" t="n">
         <v>5</v>
@@ -14545,16 +14545,16 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>91683</v>
+        <v>91684</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0.006598449748578204</v>
+        <v>0.006609428866296304</v>
       </c>
       <c r="E64" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>66160</v>
@@ -14572,7 +14572,7 @@
         <v>5139</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -14588,7 +14588,7 @@
         <v>0</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>-0.1175463281088097</v>
+        <v>-0.1175559530561494</v>
       </c>
       <c r="E65" t="n">
         <v>5</v>
@@ -17584,7 +17584,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -20466,7 +20466,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -23894,16 +23894,16 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>233122</v>
+        <v>241398</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0.0123151211971201</v>
+        <v>0.0482530418696751</v>
       </c>
       <c r="E64" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>152356</v>
@@ -23918,10 +23918,10 @@
         <v>0.5020166198424866</v>
       </c>
       <c r="J64" t="n">
-        <v>17026</v>
+        <v>17051</v>
       </c>
       <c r="K64" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -23937,7 +23937,7 @@
         <v>0</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>0.8526908657269584</v>
+        <v>0.789173895392671</v>
       </c>
       <c r="E65" t="n">
         <v>5</v>
@@ -26946,7 +26946,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -30374,16 +30374,16 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>157996</v>
+        <v>158307</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0.002430002601308268</v>
+        <v>0.004403190092187827</v>
       </c>
       <c r="E64" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>135985</v>
@@ -30398,10 +30398,10 @@
         <v>0.0004769417030487581</v>
       </c>
       <c r="J64" t="n">
-        <v>11568</v>
+        <v>11577</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
@@ -30417,7 +30417,7 @@
         <v>0</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>-0.2046380921035976</v>
+        <v>-0.2062006102067502</v>
       </c>
       <c r="E65" t="n">
         <v>5</v>
@@ -33413,7 +33413,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -36073,7 +36073,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -37697,7 +37697,7 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -40283,7 +40283,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>26891</v>
@@ -43859,16 +43859,16 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>88777</v>
+        <v>88890</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0.01884432202903541</v>
+        <v>0.0201411602685488</v>
       </c>
       <c r="E64" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>63879</v>
@@ -43886,7 +43886,7 @@
         <v>5631</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -43902,7 +43902,7 @@
         <v>0</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>1.667751782556293</v>
+        <v>1.664360445494431</v>
       </c>
       <c r="E65" t="n">
         <v>5</v>
@@ -46898,7 +46898,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -7402,7 +7402,7 @@
         <v>13439</v>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -23921,7 +23921,7 @@
         <v>17051</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65">
@@ -30401,7 +30401,7 @@
         <v>11577</v>
       </c>
       <c r="K64" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65">
@@ -43886,7 +43886,7 @@
         <v>5631</v>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -23921,7 +23921,7 @@
         <v>17051</v>
       </c>
       <c r="K64" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="65">
@@ -30401,7 +30401,7 @@
         <v>11577</v>
       </c>
       <c r="K64" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="65">
@@ -43886,7 +43886,7 @@
         <v>5631</v>
       </c>
       <c r="K64" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -3799,7 +3799,7 @@
         <v>0.03468007629616785</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -7384,7 +7384,7 @@
         <v>0.0007184296898450456</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F64" t="n">
         <v>103148</v>
@@ -7399,10 +7399,10 @@
         <v>0.01866855841391928</v>
       </c>
       <c r="J64" t="n">
-        <v>13439</v>
+        <v>13440</v>
       </c>
       <c r="K64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -10969,7 +10969,7 @@
         <v>0.01746157061254818</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F64" t="n">
         <v>41946</v>
@@ -14554,7 +14554,7 @@
         <v>0.006609428866296304</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F64" t="n">
         <v>66160</v>
@@ -14572,7 +14572,7 @@
         <v>5139</v>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65">
@@ -17584,7 +17584,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -20466,7 +20466,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -23903,7 +23903,7 @@
         <v>0.0482530418696751</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F64" t="n">
         <v>152356</v>
@@ -23918,10 +23918,10 @@
         <v>0.5020166198424866</v>
       </c>
       <c r="J64" t="n">
-        <v>17051</v>
+        <v>17069</v>
       </c>
       <c r="K64" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -26946,7 +26946,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -30383,7 +30383,7 @@
         <v>0.004403190092187827</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F64" t="n">
         <v>135985</v>
@@ -30398,10 +30398,10 @@
         <v>0.0004769417030487581</v>
       </c>
       <c r="J64" t="n">
-        <v>11577</v>
+        <v>11591</v>
       </c>
       <c r="K64" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -33413,7 +33413,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -36073,7 +36073,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -37697,7 +37697,7 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -40283,7 +40283,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F64" t="n">
         <v>26891</v>
@@ -43868,7 +43868,7 @@
         <v>0.0201411602685488</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F64" t="n">
         <v>63879</v>
@@ -43886,7 +43886,7 @@
         <v>5631</v>
       </c>
       <c r="K64" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65">
@@ -46898,7 +46898,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -3799,7 +3799,7 @@
         <v>0.03468007629616785</v>
       </c>
       <c r="E64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -7384,7 +7384,7 @@
         <v>0.0007184296898450456</v>
       </c>
       <c r="E64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F64" t="n">
         <v>103148</v>
@@ -7402,7 +7402,7 @@
         <v>13440</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
@@ -10969,7 +10969,7 @@
         <v>0.01746157061254818</v>
       </c>
       <c r="E64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F64" t="n">
         <v>41946</v>
@@ -10987,7 +10987,7 @@
         <v>4516</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -14554,7 +14554,7 @@
         <v>0.006609428866296304</v>
       </c>
       <c r="E64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F64" t="n">
         <v>66160</v>
@@ -14572,7 +14572,7 @@
         <v>5139</v>
       </c>
       <c r="K64" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="65">
@@ -17584,7 +17584,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -20466,7 +20466,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -23903,7 +23903,7 @@
         <v>0.0482530418696751</v>
       </c>
       <c r="E64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F64" t="n">
         <v>152356</v>
@@ -23912,16 +23912,16 @@
         <v>4948</v>
       </c>
       <c r="H64" t="n">
-        <v>70983</v>
+        <v>73479</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0.5020166198424866</v>
+        <v>0.5184390770263246</v>
       </c>
       <c r="J64" t="n">
         <v>17069</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65">
@@ -23952,7 +23952,7 @@
         <v>0</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>-0.8801026777696496</v>
+        <v>-0.8813994098352131</v>
       </c>
       <c r="J65" t="n">
         <v>9274</v>
@@ -26946,7 +26946,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -30383,7 +30383,7 @@
         <v>0.004403190092187827</v>
       </c>
       <c r="E64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F64" t="n">
         <v>135985</v>
@@ -30401,7 +30401,7 @@
         <v>11591</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
@@ -33413,7 +33413,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -36073,7 +36073,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -37697,7 +37697,7 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -40283,7 +40283,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F64" t="n">
         <v>26891</v>
@@ -43868,7 +43868,7 @@
         <v>0.0201411602685488</v>
       </c>
       <c r="E64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F64" t="n">
         <v>63879</v>
@@ -43886,7 +43886,7 @@
         <v>5631</v>
       </c>
       <c r="K64" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="65">
@@ -46898,7 +46898,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -3799,7 +3799,7 @@
         <v>0.03468007629616785</v>
       </c>
       <c r="E64" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -7384,7 +7384,7 @@
         <v>0.0007184296898450456</v>
       </c>
       <c r="E64" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F64" t="n">
         <v>103148</v>
@@ -7399,10 +7399,10 @@
         <v>0.01866855841391928</v>
       </c>
       <c r="J64" t="n">
-        <v>13440</v>
+        <v>13445</v>
       </c>
       <c r="K64" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -10969,7 +10969,7 @@
         <v>0.01746157061254818</v>
       </c>
       <c r="E64" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F64" t="n">
         <v>41946</v>
@@ -14554,7 +14554,7 @@
         <v>0.006609428866296304</v>
       </c>
       <c r="E64" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F64" t="n">
         <v>66160</v>
@@ -14569,10 +14569,10 @@
         <v>0.0008733098443099346</v>
       </c>
       <c r="J64" t="n">
-        <v>5139</v>
+        <v>5148</v>
       </c>
       <c r="K64" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -17584,7 +17584,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -20466,7 +20466,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -23903,7 +23903,7 @@
         <v>0.0482530418696751</v>
       </c>
       <c r="E64" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F64" t="n">
         <v>152356</v>
@@ -23918,10 +23918,10 @@
         <v>0.5184390770263246</v>
       </c>
       <c r="J64" t="n">
-        <v>17069</v>
+        <v>17078</v>
       </c>
       <c r="K64" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -26946,7 +26946,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -30383,7 +30383,7 @@
         <v>0.004403190092187827</v>
       </c>
       <c r="E64" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F64" t="n">
         <v>135985</v>
@@ -30398,10 +30398,10 @@
         <v>0.0004769417030487581</v>
       </c>
       <c r="J64" t="n">
-        <v>11591</v>
+        <v>11597</v>
       </c>
       <c r="K64" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -33413,7 +33413,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -36073,7 +36073,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -37697,7 +37697,7 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -40283,7 +40283,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F64" t="n">
         <v>26891</v>
@@ -40301,7 +40301,7 @@
         <v>1847</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
@@ -43868,7 +43868,7 @@
         <v>0.0201411602685488</v>
       </c>
       <c r="E64" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F64" t="n">
         <v>63879</v>
@@ -43883,10 +43883,10 @@
         <v>0.001236713160819675</v>
       </c>
       <c r="J64" t="n">
-        <v>5631</v>
+        <v>5639</v>
       </c>
       <c r="K64" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -46898,7 +46898,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -14572,7 +14572,7 @@
         <v>5148</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -23918,7 +23918,7 @@
         <v>0.5184390770263246</v>
       </c>
       <c r="J64" t="n">
-        <v>17078</v>
+        <v>17090</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -30401,7 +30401,7 @@
         <v>11597</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -40298,10 +40298,10 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>1847</v>
+        <v>1850</v>
       </c>
       <c r="K64" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroJIM.xlsx
+++ b/regionais/registroJIM.xlsx
@@ -7399,10 +7399,10 @@
         <v>0.01866855841391928</v>
       </c>
       <c r="J64" t="n">
-        <v>13445</v>
+        <v>13447</v>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -14569,10 +14569,10 @@
         <v>0.0008733098443099346</v>
       </c>
       <c r="J64" t="n">
-        <v>5148</v>
+        <v>5150</v>
       </c>
       <c r="K64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -23918,7 +23918,7 @@
         <v>0.5184390770263246</v>
       </c>
       <c r="J64" t="n">
-        <v>17090</v>
+        <v>17100</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -30398,7 +30398,7 @@
         <v>0.0004769417030487581</v>
       </c>
       <c r="J64" t="n">
-        <v>11597</v>
+        <v>11605</v>
       </c>
       <c r="K64" t="n">
         <v>1</v>
@@ -43886,7 +43886,7 @@
         <v>5639</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
